--- a/VerveStacks_IRL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IRL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IRL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{945D8568-7936-43ED-AAC4-77C6AF304954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4A5A9D-98C2-4ABA-9B03-D6246E9351F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="460">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1505,6 +1505,9 @@
   </si>
   <si>
     <t>Transformer: e_w88144450-220 → e_w88144450-400</t>
+  </si>
+  <si>
+    <t>e_IE11-220,e_IE6-220,e_w104388595-220,e_w104388599-220,e_w1154822210-220,e_w147525695-220,e_w207331199-220,e_w207339053-220,e_w207339053-400,e_w208124159-220,e_w255668124-220,e_w264275258-220,e_w264275258-275,e_w35150701-220,e_w361261945-220,e_w516651650-220,e_w714018181-220,e_w79803767-220</t>
   </si>
 </sst>
 </file>
@@ -3398,7 +3401,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_IE11-220,e_IE6-220,e_w104388595-220,e_w104388599-220,e_w1154822210-220,e_w147525695-220,e_w207331199-220,e_w207339053-220,e_w207339053-400,e_w208124159-220,e_w255668124-220,e_w264275258-220,e_w264275258-275,e_w35150701-220,e_w361261945-220,e_w516651650-220,e_w714018181-220,e_w79803767-220</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3420,7 +3423,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_IE11-220,e_IE6-220,e_w104388595-220,e_w104388599-220,e_w1154822210-220,e_w147525695-220,e_w207331199-220,e_w207339053-220,e_w207339053-400,e_w208124159-220,e_w255668124-220,e_w264275258-220,e_w264275258-275,e_w35150701-220,e_w361261945-220,e_w516651650-220,e_w714018181-220,e_w79803767-220</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3435,7 +3438,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
